--- a/data/trans_orig/CAGE-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2007</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1924</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,62 +881,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2641</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>10442</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2641</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>8759</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,62 +994,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>7101</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>682070</t>
+          <t>682132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>692949</t>
+          <t>692300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>686455</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>688351</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1371052</t>
+          <t>1371055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1381302</t>
+          <t>1381307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,47 +1450,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>947589</t>
+          <t>947902</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>958717</t>
+          <t>958819</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>961583</t>
+          <t>962631</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1914873</t>
+          <t>1914339</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1926310</t>
+          <t>1926274</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1984,97 +1984,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>665750</t>
+          <t>665251</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>675644</t>
+          <t>675796</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>681957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>683841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1349173</t>
+          <t>1347850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1359452</t>
+          <t>1359413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -2440,82 +2440,82 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>927125</t>
+          <t>926965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>939232</t>
+          <t>938958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1021437</t>
+          <t>1021858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1034964</t>
+          <t>1034921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1954815</t>
+          <t>1954693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1972039</t>
+          <t>1972257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>30430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3237641</t>
+          <t>3238497</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3259498</t>
+          <t>3259529</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3361538</t>
+          <t>3360830</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3375477</t>
+          <t>3374871</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,47 +3398,47 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>6608034</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>6631537</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>99,89%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>6607397</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>6630932</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2012</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,62 +3845,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3742</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3658</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>688236</t>
+          <t>687140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>699120</t>
+          <t>698868</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>692002</t>
+          <t>691872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1383624</t>
+          <t>1383550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1395417</t>
+          <t>1395525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>18358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>15929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>991578</t>
+          <t>989723</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1010671</t>
+          <t>1010926</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1027231</t>
+          <t>1026197</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2023640</t>
+          <t>2022821</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2041839</t>
+          <t>2041887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,62 +4983,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6061</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6889</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15575</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18598</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>728621</t>
+          <t>728182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>746946</t>
+          <t>746857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>771968</t>
+          <t>772175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1505414</t>
+          <t>1504579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1523537</t>
+          <t>1522840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -5517,82 +5517,82 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>3930</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>10896</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>3930</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13205</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>909587</t>
+          <t>909012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>931442</t>
+          <t>931559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1044297</t>
+          <t>1044431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1959221</t>
+          <t>1958564</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1982266</t>
+          <t>1981043</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,42 +6136,42 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>8882</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>16456</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>8882</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>4554</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>17087</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32783</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>35061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51869</t>
+          <t>48962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>29203</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56115</t>
+          <t>56191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3340833</t>
+          <t>3342445</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3376500</t>
+          <t>3376774</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3546904</t>
+          <t>3546864</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3556323</t>
+          <t>3556320</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6893666</t>
+          <t>6895004</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6929953</t>
+          <t>6929706</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2016</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,97 +6887,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,62 +7035,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2119</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>7425</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2119</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6522</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,42 +7168,42 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>6420</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>13248</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>0,98%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>6420</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>2232</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>12606</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>672215</t>
+          <t>671731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>666262</t>
+          <t>666206</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1331916</t>
+          <t>1331418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1343636</t>
+          <t>1344156</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25457</t>
+          <t>25124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28509</t>
+          <t>27748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>987525</t>
+          <t>987396</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1008568</t>
+          <t>1008594</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1034488</t>
+          <t>1034839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1041986</t>
+          <t>1041980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2026242</t>
+          <t>2026745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2049624</t>
+          <t>2048977</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -8025,97 +8025,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8138,97 +8138,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>744699</t>
+          <t>744248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>756340</t>
+          <t>756333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>782966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>785011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1529518</t>
+          <t>1529661</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1541428</t>
+          <t>1541397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8594,82 +8594,82 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4830</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4916</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27442</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>917277</t>
+          <t>916908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>930653</t>
+          <t>931231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1023995</t>
+          <t>1023328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1037683</t>
+          <t>1037838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1946144</t>
+          <t>1945671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1966375</t>
+          <t>1966878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>23565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49083</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24246</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65528</t>
+          <t>62976</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3328454</t>
+          <t>3328658</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3357958</t>
+          <t>3358339</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3516511</t>
+          <t>3517413</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3534797</t>
+          <t>3534672</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6853576</t>
+          <t>6855302</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6887541</t>
+          <t>6888494</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2023</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,62 +10112,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4481</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,62 +10225,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4507</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1273</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>4844</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>325515</t>
+          <t>325445</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331707</t>
+          <t>331717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155105</t>
+          <t>155183</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>484121</t>
+          <t>483841</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>490916</t>
+          <t>491118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19010</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10666,34 +10666,34 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4140</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4754</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>459604</t>
+          <t>459366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>471937</t>
+          <t>472040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>188597</t>
+          <t>188617</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>197817</t>
+          <t>198000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>652465</t>
+          <t>652555</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>667669</t>
+          <t>667704</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -11102,97 +11102,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14858</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>2228</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14783</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>12925</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>12836</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>335</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309778</t>
+          <t>309297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>318963</t>
+          <t>318919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>353634</t>
+          <t>353982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>669348</t>
+          <t>670376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>687049</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19732</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>414874</t>
+          <t>414432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>432525</t>
+          <t>432379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>282360</t>
+          <t>281716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287642</t>
+          <t>287846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>699639</t>
+          <t>700214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>719030</t>
+          <t>718838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31732</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18594</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25471</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>450</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28032</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1524803</t>
+          <t>1523399</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1548782</t>
+          <t>1547632</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>994878</t>
+          <t>993489</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1011772</t>
+          <t>1011904</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2526989</t>
+          <t>2526518</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2556512</t>
+          <t>2558404</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Habitat-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>682132</t>
+          <t>681538</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>692300</t>
+          <t>692954</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1371055</t>
+          <t>1369633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1381307</t>
+          <t>1381303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>947902</t>
+          <t>947672</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>958819</t>
+          <t>958833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>962631</t>
+          <t>962583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1914339</t>
+          <t>1915080</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1926274</t>
+          <t>1926606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>665251</t>
+          <t>665732</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>675796</t>
+          <t>675837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1347850</t>
+          <t>1348982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1359413</t>
+          <t>1359559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>879</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>926965</t>
+          <t>926789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>938958</t>
+          <t>938826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1021858</t>
+          <t>1021629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1034921</t>
+          <t>1035396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1954693</t>
+          <t>1955287</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1972257</t>
+          <t>1972241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3238497</t>
+          <t>3238570</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3259529</t>
+          <t>3259691</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3368,77 +3368,77 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>3369908</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>3360686</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3374565</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>6606768</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>6630767</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>3369908</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>3360830</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>3374871</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>6608034</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>6631537</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,39 +4051,39 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5178</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>687140</t>
+          <t>687887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>698868</t>
+          <t>699182</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>691872</t>
+          <t>691994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1383550</t>
+          <t>1382737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1395525</t>
+          <t>1395454</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18358</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>989723</t>
+          <t>992156</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1010926</t>
+          <t>1011364</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1026197</t>
+          <t>1027285</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2022821</t>
+          <t>2022244</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2041887</t>
+          <t>2042690</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,49 +5189,49 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5029</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4999</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>728182</t>
+          <t>728770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>746857</t>
+          <t>746674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>772175</t>
+          <t>772145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1504579</t>
+          <t>1504236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1522840</t>
+          <t>1522763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27617</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29509</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>909012</t>
+          <t>909475</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>931559</t>
+          <t>931563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1044431</t>
+          <t>1044952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1958564</t>
+          <t>1958875</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1981043</t>
+          <t>1981543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32989</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35061</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48962</t>
+          <t>50588</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>28378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56191</t>
+          <t>56898</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3342445</t>
+          <t>3341906</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3376774</t>
+          <t>3377081</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3546864</t>
+          <t>3546084</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3556320</t>
+          <t>3556330</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6895004</t>
+          <t>6894514</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6929706</t>
+          <t>6929568</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>660263</t>
+          <t>661615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>671731</t>
+          <t>672404</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>666206</t>
+          <t>666528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1331418</t>
+          <t>1331114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1344156</t>
+          <t>1343956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27748</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>987396</t>
+          <t>987561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1008594</t>
+          <t>1008207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1034839</t>
+          <t>1034314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1041980</t>
+          <t>1041985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2026745</t>
+          <t>2027761</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2048977</t>
+          <t>2049584</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>744248</t>
+          <t>745421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>756333</t>
+          <t>756330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1529661</t>
+          <t>1529592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1541397</t>
+          <t>1541390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>19268</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27581</t>
+          <t>27874</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>916908</t>
+          <t>916771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>931231</t>
+          <t>930757</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1023328</t>
+          <t>1023090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1037838</t>
+          <t>1037793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1945671</t>
+          <t>1944846</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1966878</t>
+          <t>1965414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>47579</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62976</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3328658</t>
+          <t>3330290</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3358339</t>
+          <t>3358349</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3517413</t>
+          <t>3518342</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3534672</t>
+          <t>3535282</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6855302</t>
+          <t>6854957</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6888494</t>
+          <t>6887685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -10004,12 +10004,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,22 +10029,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -10195,12 +10195,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>329649</t>
+          <t>349946</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>325445</t>
+          <t>346041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331717</t>
+          <t>351941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,27 +10333,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>158790</t>
+          <t>171764</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155183</t>
+          <t>168387</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>488439</t>
+          <t>521710</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>483841</t>
+          <t>517292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>491118</t>
+          <t>524324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>590</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -10651,12 +10651,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -10686,12 +10686,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,17 +10711,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>644</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>467278</t>
+          <t>491304</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>459366</t>
+          <t>483991</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>472040</t>
+          <t>496521</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>194703</t>
+          <t>216117</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>188617</t>
+          <t>209150</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>198000</t>
+          <t>219293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>661980</t>
+          <t>707423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>652555</t>
+          <t>698671</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>667704</t>
+          <t>713601</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>200071</t>
+          <t>221813</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200071</t>
+          <t>221813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200071</t>
+          <t>221813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>676827</t>
+          <t>722537</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>676827</t>
+          <t>722537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>676827</t>
+          <t>722537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -11210,69 +11210,69 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
           <t>2,47%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>689</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>315852</t>
+          <t>345294</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309297</t>
+          <t>335645</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>318919</t>
+          <t>350588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>364852</t>
+          <t>189256</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>353982</t>
+          <t>178161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>192205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>680705</t>
+          <t>534549</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>670376</t>
+          <t>523777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>540977</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11967</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>756</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>425453</t>
+          <t>445547</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>414432</t>
+          <t>435379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>432379</t>
+          <t>453727</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>285856</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>281716</t>
+          <t>294380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287846</t>
+          <t>305832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>711309</t>
+          <t>748089</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>700214</t>
+          <t>735062</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>718838</t>
+          <t>757173</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,22 +12235,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>37027</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>29136</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1538231</t>
+          <t>1632092</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1523399</t>
+          <t>1617778</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1547632</t>
+          <t>1643478</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1004202</t>
+          <t>879679</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>993489</t>
+          <t>867843</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1011904</t>
+          <t>886578</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2542434</t>
+          <t>2511770</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2526518</t>
+          <t>2495242</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2558404</t>
+          <t>2525557</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
